--- a/outputs/SAN/FC/SN3600B_FC/Config2_SN3600B_FC_Switch_EVALUATED_BOQ_Evaluated BOQ_Partner_Portal.xlsx
+++ b/outputs/SAN/FC/SN3600B_FC/Config2_SN3600B_FC_Switch_EVALUATED_BOQ_Evaluated BOQ_Partner_Portal.xlsx
@@ -829,7 +829,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G9"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -934,7 +934,7 @@
     </row>
     <row r="5">
       <c r="A5" s="9" t="str">
-        <v>HX2M2E</v>
+        <v>HA113A1</v>
       </c>
       <c r="B5" s="10">
         <v>1</v>
@@ -943,13 +943,13 @@
         <v>1</v>
       </c>
       <c r="D5" s="11" t="str">
-        <v>HPE 3 Year Tech Care Basic wCDMR SN3600B 24/8 8p 32Gb SW SFP Switch Service</v>
+        <v>HPE Installation Service</v>
       </c>
       <c r="E5" s="12">
-        <v>950</v>
+        <v>0</v>
       </c>
       <c r="F5" s="13">
-        <v>950</v>
+        <v>0</v>
       </c>
       <c r="G5" s="11" t="str">
         <v>CLIC_ACCEPTED_EXACT_MANIFEST</v>
@@ -957,7 +957,7 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="str">
-        <v>U5988E</v>
+        <v>HA113A1 5GA</v>
       </c>
       <c r="B6" s="5">
         <v>1</v>
@@ -966,44 +966,90 @@
         <v>1</v>
       </c>
       <c r="D6" s="6" t="str">
-        <v>HPE Installation Storage Switches Service</v>
+        <v>HPE LowEnd SAN/Edge Switch/HAFM Inst SVC</v>
       </c>
       <c r="E6" s="7">
-        <v>480</v>
+        <v>537</v>
       </c>
       <c r="F6" s="8">
-        <v>480</v>
+        <v>537</v>
       </c>
       <c r="G6" s="6" t="str">
         <v>CLIC_ACCEPTED_EXACT_MANIFEST</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="str">
+      <c r="A7" s="9" t="str">
+        <v>HU4B3A3</v>
+      </c>
+      <c r="B7" s="10">
+        <v>1</v>
+      </c>
+      <c r="C7" s="10">
+        <v>1</v>
+      </c>
+      <c r="D7" s="11" t="str">
+        <v>HPE 3Y Tech Care Basic with Defective Media Retention Service</v>
+      </c>
+      <c r="E7" s="12">
+        <v>0</v>
+      </c>
+      <c r="F7" s="13">
+        <v>0</v>
+      </c>
+      <c r="G7" s="11" t="str">
+        <v>CLIC_ACCEPTED_EXACT_MANIFEST</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="str">
+        <v>HU4B3A3 ZTL</v>
+      </c>
+      <c r="B8" s="5">
+        <v>1</v>
+      </c>
+      <c r="C8" s="5">
+        <v>1</v>
+      </c>
+      <c r="D8" s="6" t="str">
+        <v>HPE SN3600B 24/8 8p 32G Swch Support</v>
+      </c>
+      <c r="E8" s="7">
+        <v>186</v>
+      </c>
+      <c r="F8" s="8">
+        <v>186</v>
+      </c>
+      <c r="G8" s="6" t="str">
+        <v>CLIC_ACCEPTED_EXACT_MANIFEST</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="str">
         <v/>
       </c>
-      <c r="B7" s="14" t="str">
+      <c r="B9" s="14" t="str">
         <v/>
       </c>
-      <c r="C7" s="15" t="str">
+      <c r="C9" s="15" t="str">
         <v>CONFIG #1 SUBTOTAL:</v>
       </c>
-      <c r="D7" s="14" t="str">
+      <c r="D9" s="14" t="str">
         <v/>
       </c>
-      <c r="E7" s="16" t="str">
+      <c r="E9" s="16" t="str">
         <v/>
       </c>
-      <c r="F7" s="16">
-        <v>62636</v>
-      </c>
-      <c r="G7" s="14" t="str">
+      <c r="F9" s="16">
+        <v>61929</v>
+      </c>
+      <c r="G9" s="14" t="str">
         <v>1 Nodes Ready for Portal Feed</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G9"/>
   </ignoredErrors>
 </worksheet>
 </file>